--- a/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_05_workbook.xlsx
+++ b/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_05_workbook.xlsx
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1350</v>
+        <v>1600</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03519362211227417</v>
+        <v>0.0309972669929266</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7540740740740741</v>
+        <v>0.741875</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1155555555555556</v>
+        <v>0.11125</v>
       </c>
     </row>
     <row r="3">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1381</v>
+        <v>1490</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06496416032314301</v>
+        <v>0.05929079279303551</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7538015930485156</v>
+        <v>0.7463087248322148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09558291093410572</v>
+        <v>0.1053691275167785</v>
       </c>
     </row>
     <row r="4">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1406</v>
+        <v>1330</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09642893821001053</v>
+        <v>0.09012799710035324</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7460881934566145</v>
+        <v>0.7390977443609023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1081081081081081</v>
+        <v>0.1240601503759398</v>
       </c>
     </row>
     <row r="5">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1437</v>
+        <v>1226</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1488106697797775</v>
+        <v>0.1444284021854401</v>
       </c>
       <c r="D5" t="n">
-        <v>0.732080723729993</v>
+        <v>0.7553017944535073</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1245650661099513</v>
+        <v>0.1044045676998369</v>
       </c>
     </row>
     <row r="6">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1426</v>
+        <v>1354</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4894146025180817</v>
+        <v>0.5339727997779846</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7503506311360448</v>
+        <v>0.7548005908419497</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1164095371669004</v>
+        <v>0.1159527326440177</v>
       </c>
     </row>
   </sheetData>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Cramer's V=0.0277 between PD_RISK_BAND and historical NAME_CONTRACT_STATUS (chi2=16.09, p=0.1873) across 7,000 matched real rows.</t>
+          <t>Cramer's V=0.0234 between PD_RISK_BAND and historical NAME_CONTRACT_STATUS (chi2=11.47, p=0.4891) across 7,000 matched real rows.</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
